--- a/Result/profitability/3230.xlsx
+++ b/Result/profitability/3230.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3350000000000001</v>
+        <v>-0.3500000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>7.53375</v>
+        <v>7.415000000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2887500000000001</v>
+        <v>-0.3637500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>8.620000000000001</v>
+        <v>8.7225</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.39</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1175000000000001</v>
+        <v>-0.1712500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>11.02375</v>
+        <v>9.055</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.05</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09250000000000008</v>
+        <v>-0.09500000000000006</v>
       </c>
       <c r="N5" t="n">
-        <v>9.61875</v>
+        <v>10.28125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.51</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.08625000000000008</v>
+        <v>-0.1037500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>9.407500000000001</v>
+        <v>8.68375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.24</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.06125000000000008</v>
+        <v>-0.07875000000000007</v>
       </c>
       <c r="N7" t="n">
-        <v>9.31</v>
+        <v>8.90875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.12</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.02125000000000007</v>
+        <v>-0.03750000000000006</v>
       </c>
       <c r="N8" t="n">
-        <v>10.325</v>
+        <v>10.26625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>-0.63</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03124999999999992</v>
+        <v>0.03124999999999993</v>
       </c>
       <c r="N10" t="n">
         <v>10.45</v>
@@ -1772,7 +1772,7 @@
         <v>-0.64</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.03750000000000007</v>
+        <v>-0.03750000000000006</v>
       </c>
       <c r="N11" t="n">
         <v>8.856249999999999</v>
@@ -2026,7 +2026,7 @@
         <v>-0.9399999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3837500000000001</v>
+        <v>-0.38375</v>
       </c>
       <c r="N13" t="n">
         <v>6.885</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3230</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>103</v>
+      </c>
+      <c r="D75" t="n">
+        <v>99</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-46</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-45.16%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-49</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-49</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.3825000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>6.34625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.1299999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2888888888888888</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.4699999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1090487238979118</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.01999999999999991</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.03571428571428559</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-3.63013698630137</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
